--- a/XBRL-template-MPERS/backup-originals/Company/05-SOCI-BeforeTax.xlsx
+++ b/XBRL-template-MPERS/backup-originals/Company/05-SOCI-BeforeTax.xlsx
@@ -643,10 +643,18 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Total comprehensive income</t>
-        </is>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>*Total comprehensive income</t>
+        </is>
+      </c>
+      <c r="B28">
+        <f>1*B27+1*B11</f>
+        <v/>
+      </c>
+      <c r="C28">
+        <f>1*C27+1*C11</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -677,11 +685,11 @@
         </is>
       </c>
       <c r="B32">
-        <f>1*B27+1*B30+1*B11+1*B31</f>
+        <f>1*B30+1*B31</f>
         <v/>
       </c>
       <c r="C32">
-        <f>1*C27+1*C30+1*C11+1*C31</f>
+        <f>1*C30+1*C31</f>
         <v/>
       </c>
     </row>
